--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0010.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0010.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Nó nhắc nhở ta rằng ta không còn cô đơn nữa.</t>
+          <t>Nó nhắc nhở tao rằng tao không còn cô đơn nữa.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Cứ gọi ta là {PlayerName} đi.</t>
+          <t>Cứ gọi tao là {PlayerName} đi.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Nếu phát hiện điều gì, ta sẽ báo ngay cho cậu. Rồi chúng ta sẽ bàn bước tiếp theo.</t>
+          <t>Nếu phát hiện điều gì, tao sẽ báo ngay cho cậu. Rồi chúng ta sẽ bàn bước tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Ngoài Lời Thề Huyết ước, nếu còn điều gì khác cậu muốn... hãy đến tìm tớ ở Lâu đài Porto-Veno.</t>
+          <t>Ngoài Lời Thề Huyết ước, nếu còn điều gì khác cậu muốn... hãy đến tìm tớ ở Porto-Veno Castle.</t>
         </is>
       </c>
     </row>
